--- a/validation/Catalog_check/data/target_list_filtered.xlsx
+++ b/validation/Catalog_check/data/target_list_filtered.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WBS\Desktop\EXOPLANET WORK\006 NATSUME\validation\Catalog_check\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518B1696-2DAA-4BC8-A0E6-8BCD5378569A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5600029F-77A6-46F0-86B4-E2E99FEFD568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
   <si>
     <t>KOI_inner</t>
   </si>
@@ -243,12 +243,6 @@
     <t>10.3847/1538-3881/ab65c8</t>
   </si>
   <si>
-    <t>mutual_inclination</t>
-  </si>
-  <si>
-    <t>mutual_inclination_err</t>
-  </si>
-  <si>
     <t>Masuda+13</t>
   </si>
   <si>
@@ -306,36 +300,12 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>ew_converted</t>
-  </si>
-  <si>
-    <t>ew_converted, Kepler LC Only</t>
-  </si>
-  <si>
-    <t>ew_converted, Test4</t>
-  </si>
-  <si>
-    <t>Configuration A</t>
-  </si>
-  <si>
-    <t>ew_converted, TTV Only</t>
-  </si>
-  <si>
-    <t>ew_converted, High mutual inclination</t>
-  </si>
-  <si>
-    <t>ew_converted, Test3</t>
-  </si>
-  <si>
     <t>peri_convention</t>
   </si>
   <si>
     <t>PyDynamicaLC</t>
   </si>
   <si>
-    <t>RadVel, juliet</t>
-  </si>
-  <si>
     <t>peri_offset</t>
   </si>
   <si>
@@ -345,7 +315,34 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>REBOUND</t>
+    <t xml:space="preserve">Levenberg-Marquardt </t>
+  </si>
+  <si>
+    <t>REBOUND+WHFAST</t>
+  </si>
+  <si>
+    <t>Kokubo+04</t>
+  </si>
+  <si>
+    <t>TTV dynamical model solution</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Test 4 (Holczer catalog) solution</t>
+  </si>
+  <si>
+    <t>Kepler LC only solution</t>
+  </si>
+  <si>
+    <t>Configuration A solution</t>
+  </si>
+  <si>
+    <t>TTV only solution</t>
+  </si>
+  <si>
+    <t>Coplanar solution</t>
   </si>
 </sst>
 </file>
@@ -387,10 +384,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -671,15 +669,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AL15"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="12" width="10.3828125" customWidth="1"/>
     <col min="13" max="13" width="10.3828125" style="1" customWidth="1"/>
-    <col min="14" max="41" width="10.3828125" customWidth="1"/>
+    <col min="14" max="39" width="10.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -774,34 +772,28 @@
         <v>22</v>
       </c>
       <c r="AF1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AG1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AH1" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="AI1" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="AJ1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AK1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="AL1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>137.01</v>
       </c>
@@ -833,10 +825,10 @@
         <v>5.7000000000000005E-7</v>
       </c>
       <c r="K2">
-        <v>14.8589225</v>
+        <v>14.858918729999999</v>
       </c>
       <c r="L2" s="2">
-        <v>9.2E-6</v>
+        <v>7.4000000000000003E-6</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>57</v>
@@ -848,12 +840,12 @@
         <v>1</v>
       </c>
       <c r="P2">
-        <f>K2/I2*(N2-O2)/N2 - 1</f>
-        <v>-2.7756227683072732E-2</v>
+        <f t="shared" ref="P2:P15" si="0">K2/I2*(N2-O2)/N2 - 1</f>
+        <v>-2.7756474360382088E-2</v>
       </c>
       <c r="Q2">
-        <f>1/ABS(N2/K2-(N2-O2)/I2)</f>
-        <v>267.66826295098014</v>
+        <f t="shared" ref="Q2:Q15" si="1">1/ABS(N2/K2-(N2-O2)/I2)</f>
+        <v>267.66581621779528</v>
       </c>
       <c r="R2" t="s">
         <v>37</v>
@@ -865,13 +857,13 @@
         <v>5.4431887273256201E-2</v>
       </c>
       <c r="U2">
-        <v>5.9780685444616698E-3</v>
+        <v>5.3487981713604398E-3</v>
       </c>
       <c r="V2">
-        <v>5.16001705943007E-2</v>
+        <v>4.9712359474996998E-2</v>
       </c>
       <c r="W2">
-        <v>4.4048926117086001E-3</v>
+        <v>4.0902574251579799E-3</v>
       </c>
       <c r="X2">
         <v>3.3854098717880498E-4</v>
@@ -898,30 +890,28 @@
         <v>7.4933850537993196</v>
       </c>
       <c r="AF2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2">
+        <v>-90</v>
+      </c>
+      <c r="AH2">
         <v>0.97199999999999998</v>
       </c>
-      <c r="AK2">
+      <c r="AI2">
         <v>4.2000000000000003E-2</v>
       </c>
+      <c r="AJ2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>64</v>
+      </c>
       <c r="AL2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>248.01</v>
       </c>
@@ -968,11 +958,11 @@
         <v>1</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P12" si="0">K3/I3*(N3-O3)/N3 - 1</f>
+        <f t="shared" si="0"/>
         <v>9.8964314638061435E-3</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q12" si="1">1/ABS(N3/K3-(N3-O3)/I3)</f>
+        <f t="shared" si="1"/>
         <v>367.56405780914451</v>
       </c>
       <c r="R3" t="s">
@@ -1018,28 +1008,28 @@
         <v>41.137720438357</v>
       </c>
       <c r="AF3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="AG3">
         <v>0</v>
       </c>
-      <c r="AJ3">
+      <c r="AH3">
         <v>0.54100000000000004</v>
       </c>
-      <c r="AK3">
+      <c r="AI3">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="AL3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>90</v>
+      <c r="AJ3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>277.02</v>
       </c>
@@ -1136,28 +1126,28 @@
         <v>24.769679038597801</v>
       </c>
       <c r="AF4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
+        <v>-90</v>
+      </c>
+      <c r="AH4">
         <v>1.034</v>
       </c>
-      <c r="AK4">
+      <c r="AI4">
         <v>2.1999999999999999E-2</v>
       </c>
+      <c r="AJ4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>68</v>
+      </c>
       <c r="AL4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>775.02</v>
       </c>
@@ -1254,28 +1244,28 @@
         <v>12.118971254184901</v>
       </c>
       <c r="AF5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="AG5">
         <v>0</v>
       </c>
-      <c r="AJ5">
+      <c r="AH5">
         <v>0.63300000000000001</v>
       </c>
-      <c r="AK5">
+      <c r="AI5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="AL5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>90</v>
+      <c r="AJ5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>834.01</v>
       </c>
@@ -1372,28 +1362,28 @@
         <v>74.780772168852096</v>
       </c>
       <c r="AF6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="AG6">
         <v>0</v>
       </c>
-      <c r="AJ6">
+      <c r="AH6">
         <v>1.2290000000000001</v>
       </c>
-      <c r="AK6">
+      <c r="AI6">
         <v>6.2E-2</v>
       </c>
-      <c r="AL6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>90</v>
+      <c r="AJ6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>886.01</v>
       </c>
@@ -1490,28 +1480,28 @@
         <v>36.6940695139401</v>
       </c>
       <c r="AF7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="AG7">
         <v>0</v>
       </c>
-      <c r="AJ7">
+      <c r="AH7">
         <v>0.48399999999999999</v>
       </c>
-      <c r="AK7">
+      <c r="AI7">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="AL7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>90</v>
+      <c r="AJ7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>250.01</v>
       </c>
@@ -1519,10 +1509,10 @@
         <v>250.02</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E8">
         <v>2454966.5479330001</v>
@@ -1549,7 +1539,7 @@
         <v>2.1100000000000001E-6</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N8">
         <v>7</v>
@@ -1558,11 +1548,11 @@
         <v>2</v>
       </c>
       <c r="P8">
-        <f t="shared" ref="P8:P10" si="2">K8/I8*(N8-O8)/N8 - 1</f>
+        <f t="shared" si="0"/>
         <v>3.1963178803962045E-3</v>
       </c>
       <c r="Q8">
-        <f t="shared" ref="Q8:Q10" si="3">1/ABS(N8/K8-(N8-O8)/I8)</f>
+        <f t="shared" si="1"/>
         <v>771.02942714199673</v>
       </c>
       <c r="R8" t="s">
@@ -1608,28 +1598,28 @@
         <v>158.134464654591</v>
       </c>
       <c r="AF8" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
+        <v>-90</v>
+      </c>
+      <c r="AH8">
         <v>0.54400000000000004</v>
       </c>
-      <c r="AK8">
+      <c r="AI8">
         <v>2.5000000000000001E-2</v>
       </c>
+      <c r="AJ8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>84</v>
+      </c>
       <c r="AL8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>314.01</v>
       </c>
@@ -1637,10 +1627,10 @@
         <v>314.02</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E9">
         <v>2454955.7286669998</v>
@@ -1676,11 +1666,11 @@
         <v>2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.2464458276035852E-3</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>880.17639021524701</v>
       </c>
       <c r="R9" t="s">
@@ -1714,40 +1704,40 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="AB9">
-        <v>88.81</v>
+        <v>161</v>
       </c>
       <c r="AC9">
-        <v>0.15</v>
+        <v>27</v>
       </c>
       <c r="AD9">
-        <v>88.951999999999998</v>
+        <v>66.31</v>
       </c>
       <c r="AE9">
-        <v>8.2000000000000003E-2</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
+        <v>-90</v>
+      </c>
+      <c r="AH9">
         <v>0.55100000000000005</v>
       </c>
-      <c r="AK9">
+      <c r="AI9">
         <v>6.8000000000000005E-2</v>
       </c>
+      <c r="AJ9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>86</v>
+      </c>
       <c r="AL9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1576.01</v>
       </c>
@@ -1755,10 +1745,10 @@
         <v>1576.02</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>2454965.629828</v>
@@ -1794,11 +1784,11 @@
         <v>1</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.9621252590630327E-3</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>527.36597473439053</v>
       </c>
       <c r="R10" t="s">
@@ -1844,28 +1834,25 @@
         <v>67.371035239101502</v>
       </c>
       <c r="AF10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
+        <v>92</v>
+      </c>
+      <c r="AH10">
         <v>0.90700000000000003</v>
       </c>
-      <c r="AK10">
+      <c r="AI10">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="AL10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>96</v>
+      <c r="AJ10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
         <v>46</v>
       </c>
@@ -1914,67 +1901,64 @@
         <v>52</v>
       </c>
       <c r="T11">
-        <v>0.28699999999999998</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="U11">
-        <v>2.1999999999999999E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="V11">
-        <v>0.39200000000000002</v>
+        <v>0.375</v>
       </c>
       <c r="W11">
-        <v>2.7E-2</v>
+        <v>0.04</v>
       </c>
       <c r="X11">
-        <v>0.20799999999999999</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="Y11">
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Z11">
-        <v>0.18090000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="AA11">
-        <v>1.7999999999999999E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="AB11">
-        <v>60.6</v>
+        <v>-118.6</v>
       </c>
       <c r="AC11">
+        <v>7.2</v>
+      </c>
+      <c r="AD11">
+        <v>-153.69999999999999</v>
+      </c>
+      <c r="AE11">
         <v>6</v>
       </c>
-      <c r="AD11">
-        <v>26.1</v>
-      </c>
-      <c r="AE11">
-        <v>9.4</v>
-      </c>
       <c r="AF11" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AG11">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="AH11">
-        <v>20.8</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="AI11">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AJ11">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="AK11">
-        <v>5.1999999999999998E-2</v>
+        <v>0.05</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>66</v>
       </c>
       <c r="AL11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
         <v>48</v>
       </c>
@@ -2065,28 +2049,28 @@
         <v>49.703247242655699</v>
       </c>
       <c r="AF12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="AG12">
+        <v>-90</v>
+      </c>
+      <c r="AH12">
+        <v>1.25</v>
+      </c>
+      <c r="AI12">
         <v>0</v>
       </c>
-      <c r="AJ12">
-        <v>1.25</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
+      <c r="AJ12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>70</v>
       </c>
       <c r="AL12" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.4">
       <c r="C13" t="s">
         <v>33</v>
       </c>
@@ -2121,18 +2105,18 @@
         <v>2</v>
       </c>
       <c r="P13">
-        <f t="shared" ref="P13:P15" si="4">K13/I13*(N13-O13)/N13 - 1</f>
+        <f t="shared" si="0"/>
         <v>4.3025628114135017E-4</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q13:Q15" si="5">1/ABS(N13/K13-(N13-O13)/I13)</f>
+        <f t="shared" si="1"/>
         <v>2595.1026142789683</v>
       </c>
       <c r="R13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T13">
         <v>2.8946437162656501E-2</v>
@@ -2171,28 +2155,25 @@
         <v>12.655358163243701</v>
       </c>
       <c r="AF13" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
+        <v>91</v>
+      </c>
+      <c r="AH13">
         <v>0.33</v>
       </c>
-      <c r="AK13">
+      <c r="AI13">
         <v>0.02</v>
       </c>
-      <c r="AL13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>90</v>
+      <c r="AJ13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL13" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
         <v>33</v>
       </c>
@@ -2227,18 +2208,18 @@
         <v>1</v>
       </c>
       <c r="P14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>7.7566868408096568E-4</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>4317.6797887206985</v>
       </c>
       <c r="R14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T14">
         <v>2.52714981837453E-2</v>
@@ -2277,28 +2258,25 @@
         <v>1.88610828162814</v>
       </c>
       <c r="AF14" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
+        <v>91</v>
+      </c>
+      <c r="AH14">
         <v>0.33</v>
       </c>
-      <c r="AK14">
+      <c r="AI14">
         <v>0.02</v>
       </c>
-      <c r="AL14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>95</v>
+      <c r="AJ14" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>33</v>
       </c>
@@ -2324,7 +2302,7 @@
         <v>5.7399999999999997E-4</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -2333,18 +2311,18 @@
         <v>3</v>
       </c>
       <c r="P15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>4.84948703415089E-4</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>3453.5891903726701</v>
       </c>
       <c r="R15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T15">
         <v>6.9597303264995802E-2</v>
@@ -2383,25 +2361,22 @@
         <v>2.4989199236937498</v>
       </c>
       <c r="AF15" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
+        <v>91</v>
+      </c>
+      <c r="AH15">
         <v>0.33</v>
       </c>
-      <c r="AK15">
+      <c r="AI15">
         <v>0.02</v>
       </c>
-      <c r="AL15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>95</v>
+      <c r="AJ15" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/validation/Catalog_check/data/target_list_filtered.xlsx
+++ b/validation/Catalog_check/data/target_list_filtered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WBS\Desktop\EXOPLANET WORK\006 NATSUME\validation\Catalog_check\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5600029F-77A6-46F0-86B4-E2E99FEFD568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45125A87-6CFF-42BD-989E-0C5D7C20B8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,9 +315,6 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Levenberg-Marquardt </t>
-  </si>
-  <si>
     <t>REBOUND+WHFAST</t>
   </si>
   <si>
@@ -343,6 +340,9 @@
   </si>
   <si>
     <t>Coplanar solution</t>
+  </si>
+  <si>
+    <t>Runge-Kutta</t>
   </si>
 </sst>
 </file>
@@ -890,10 +890,10 @@
         <v>7.4933850537993196</v>
       </c>
       <c r="AF2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG2">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="AH2">
         <v>0.97199999999999998</v>
@@ -908,7 +908,7 @@
         <v>64</v>
       </c>
       <c r="AL2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.4">
@@ -1026,7 +1026,7 @@
         <v>75</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.4">
@@ -1144,7 +1144,7 @@
         <v>68</v>
       </c>
       <c r="AL4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.4">
@@ -1262,7 +1262,7 @@
         <v>75</v>
       </c>
       <c r="AL5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.4">
@@ -1380,7 +1380,7 @@
         <v>75</v>
       </c>
       <c r="AL6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.4">
@@ -1498,7 +1498,7 @@
         <v>75</v>
       </c>
       <c r="AL7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.4">
@@ -1598,7 +1598,7 @@
         <v>158.134464654591</v>
       </c>
       <c r="AF8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="AG8">
         <v>-90</v>
@@ -1616,7 +1616,7 @@
         <v>84</v>
       </c>
       <c r="AL8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.4">
@@ -1716,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="AF9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG9">
         <v>-90</v>
@@ -1734,7 +1734,7 @@
         <v>86</v>
       </c>
       <c r="AL9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.4">
@@ -1849,7 +1849,7 @@
         <v>84</v>
       </c>
       <c r="AL10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.4">
@@ -1937,7 +1937,7 @@
         <v>6</v>
       </c>
       <c r="AF11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG11">
         <v>-90</v>
@@ -1955,7 +1955,7 @@
         <v>66</v>
       </c>
       <c r="AL11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.4">
@@ -2049,7 +2049,7 @@
         <v>49.703247242655699</v>
       </c>
       <c r="AF12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG12">
         <v>-90</v>
@@ -2067,7 +2067,7 @@
         <v>70</v>
       </c>
       <c r="AL12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.4">
@@ -2170,7 +2170,7 @@
         <v>72</v>
       </c>
       <c r="AL13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.4">
@@ -2273,7 +2273,7 @@
         <v>72</v>
       </c>
       <c r="AL14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.4">
@@ -2376,7 +2376,7 @@
         <v>72</v>
       </c>
       <c r="AL15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
